--- a/Data/TestCase.xlsx
+++ b/Data/TestCase.xlsx
@@ -4,13 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10260" windowHeight="5110" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="18350" windowHeight="6800" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Get_pet" sheetId="1" r:id="rId1"/>
     <sheet name="Post_pet" sheetId="2" r:id="rId2"/>
     <sheet name="Put_pet" sheetId="3" r:id="rId3"/>
     <sheet name="Delete_pet" sheetId="4" r:id="rId4"/>
+    <sheet name="Get_pet(m)" sheetId="5" r:id="rId5"/>
+    <sheet name="Post_pet(m)" sheetId="6" r:id="rId6"/>
+    <sheet name="Put_pet(m)" sheetId="7" r:id="rId7"/>
+    <sheet name="Delete_pet(m)" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="300">
   <si>
     <t xml:space="preserve">ID </t>
   </si>
@@ -59,7 +63,7 @@
     <t>1. Gửi request GET /pet/101</t>
   </si>
   <si>
-    <t>1. API trả về mã trạng thái 200 và hiển thị thông tin của pet có ID = 101</t>
+    <t>API trả về mã trạng thái 200 và hiển thị thông tin của pet có ID = 101</t>
   </si>
   <si>
     <t>[PET02]</t>
@@ -74,7 +78,7 @@
     <t>1. Gửi request GET /pet/999999</t>
   </si>
   <si>
-    <t>1. API trả về mã trạng thái 404 và thông báo không tìm thấy dữ liệu</t>
+    <t>API trả về mã trạng thái 404 và thông báo không tìm thấy dữ liệu</t>
   </si>
   <si>
     <t>[PET03]</t>
@@ -89,7 +93,7 @@
     <t>1. Gửi request GET /pet/-1</t>
   </si>
   <si>
-    <t>1. API trả về lỗi do dữ liệu đầu vào không hợp lệ</t>
+    <t>API trả về lỗi do dữ liệu đầu vào không hợp lệ</t>
   </si>
   <si>
     <t>[PET04]</t>
@@ -104,7 +108,7 @@
     <t>1. Gửi request GET /pet/0</t>
   </si>
   <si>
-    <t>1. API trả về lỗi hoặc thông báo không tìm thấy dữ liệu</t>
+    <t>API trả về lỗi hoặc thông báo không tìm thấy dữ liệu</t>
   </si>
   <si>
     <t>[PET05]</t>
@@ -119,7 +123,7 @@
     <t>1. Gửi request GET /pet/999999999</t>
   </si>
   <si>
-    <t>1. API trả về mã trạng thái 404 hoặc thông báo không tìm thấy</t>
+    <t>API trả về mã trạng thái 404 hoặc thông báo không tìm thấy</t>
   </si>
   <si>
     <t>[PET06]</t>
@@ -134,7 +138,7 @@
     <t>1. Gửi request GET /pet/abc</t>
   </si>
   <si>
-    <t>1. API trả về mã trạng thái lỗi do sai kiểu dữ liệu</t>
+    <t>API trả về mã trạng thái lỗi do sai kiểu dữ liệu</t>
   </si>
   <si>
     <t>[PET07]</t>
@@ -149,7 +153,7 @@
     <t>1. Gửi request GET /pet/</t>
   </si>
   <si>
-    <t>1. API trả về lỗi do thiếu tham số bắt buộc</t>
+    <t>API trả về lỗi do thiếu tham số bắt buộc</t>
   </si>
   <si>
     <t>[PET08]</t>
@@ -390,6 +394,546 @@
   </si>
   <si>
     <t>1. Gửi request DELETE /pet/999999999999</t>
+  </si>
+  <si>
+    <t>Kiểm tra với ID hợp lệ và tồn tại</t>
+  </si>
+  <si>
+    <t>Hệ thống có pet với ID = 10</t>
+  </si>
+  <si>
+    <t>1. Gửi request GET /pet/10</t>
+  </si>
+  <si>
+    <t>API trả về 200 OK và thông tin pet đúng</t>
+  </si>
+  <si>
+    <t>Kiểm tra với ID hợp lệ khác</t>
+  </si>
+  <si>
+    <t>Hệ thống có pet với ID = 25</t>
+  </si>
+  <si>
+    <t>1. Gửi request GET /pet/25</t>
+  </si>
+  <si>
+    <t>API trả về 200 OK và dữ liệu chính xác</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID hợp lệ nhưng không tồn tại</t>
+  </si>
+  <si>
+    <t>Không có pet với ID = 999999</t>
+  </si>
+  <si>
+    <t>API trả về 404 Not Found</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID nhỏ nhất hợp lệ</t>
+  </si>
+  <si>
+    <t>petId = 1</t>
+  </si>
+  <si>
+    <t>1. Gửi request GET /pet/1</t>
+  </si>
+  <si>
+    <t>API trả về 200 OK (nếu tồn tại)</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID = 0 (boundary dưới)</t>
+  </si>
+  <si>
+    <t>API trả về 404 hoặc lỗi validate</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID âm</t>
+  </si>
+  <si>
+    <t>API trả về 400 Bad Request</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID rất lớn</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID = Long max</t>
+  </si>
+  <si>
+    <t>petId = 9223372036854775807</t>
+  </si>
+  <si>
+    <t>1. Gửi request GET /pet/{id}</t>
+  </si>
+  <si>
+    <t>API trả về 200 hoặc 404</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID vượt quá Long max</t>
+  </si>
+  <si>
+    <t>petId = 9223372036854775808</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID dạng số nhưng truyền dạng string</t>
+  </si>
+  <si>
+    <t>petId = "15"</t>
+  </si>
+  <si>
+    <t>1. Gửi request GET /pet/15</t>
+  </si>
+  <si>
+    <t>API trả về 200 nếu parse được</t>
+  </si>
+  <si>
+    <t>[PET11]</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID là chữ</t>
+  </si>
+  <si>
+    <t>[PET12]</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID chứa chữ và số</t>
+  </si>
+  <si>
+    <t>petId = "123abc"</t>
+  </si>
+  <si>
+    <t>1. Gửi request GET /pet/123abc</t>
+  </si>
+  <si>
+    <t>[PET13]</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID chứa ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>[PET14]</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID là số thực</t>
+  </si>
+  <si>
+    <t>petId = 1.5</t>
+  </si>
+  <si>
+    <t>1. Gửi request GET /pet/1.5</t>
+  </si>
+  <si>
+    <t>[PET15]</t>
+  </si>
+  <si>
+    <t>Kiểm tra ID là boolean</t>
+  </si>
+  <si>
+    <t>petId = true</t>
+  </si>
+  <si>
+    <t>1. Gửi request GET /pet/true</t>
+  </si>
+  <si>
+    <t>[PET16]</t>
+  </si>
+  <si>
+    <t>Không truyền petId</t>
+  </si>
+  <si>
+    <t>Không có petId</t>
+  </si>
+  <si>
+    <t>API trả về 400 hoặc 404</t>
+  </si>
+  <si>
+    <t>[PET17]</t>
+  </si>
+  <si>
+    <t>petId rỗng</t>
+  </si>
+  <si>
+    <t>petId = ""</t>
+  </si>
+  <si>
+    <t>API trả về lỗi thiếu param</t>
+  </si>
+  <si>
+    <t>[PET18]</t>
+  </si>
+  <si>
+    <t>petId chứa khoảng trắng</t>
+  </si>
+  <si>
+    <t>petId = " "</t>
+  </si>
+  <si>
+    <t>[PET19]</t>
+  </si>
+  <si>
+    <t>petId không tồn tại (random)</t>
+  </si>
+  <si>
+    <t>petId = 123456789</t>
+  </si>
+  <si>
+    <t>1. Gửi request GET /pet/123456789</t>
+  </si>
+  <si>
+    <t>Tạo pet với dữ liệu hợp lệ đầy đủ</t>
+  </si>
+  <si>
+    <t>Body hợp lệ (id, name, status, category, photoUrls, tags)</t>
+  </si>
+  <si>
+    <t>1. Gửi request POST /pet với body hợp lệ</t>
+  </si>
+  <si>
+    <t>API trả về 200 OK, pet được tạo thành công</t>
+  </si>
+  <si>
+    <t>Tạo pet với dữ liệu tối thiểu</t>
+  </si>
+  <si>
+    <t>Body chỉ có id và name</t>
+  </si>
+  <si>
+    <t>1. Gửi request POST /pet</t>
+  </si>
+  <si>
+    <t>API trả về 200 OK</t>
+  </si>
+  <si>
+    <t>Tạo pet với status hợp lệ "available"</t>
+  </si>
+  <si>
+    <t>status = "available"</t>
+  </si>
+  <si>
+    <t>Tạo pet với status "pending"</t>
+  </si>
+  <si>
+    <t>status = "pending"</t>
+  </si>
+  <si>
+    <t>Tạo pet với status "sold"</t>
+  </si>
+  <si>
+    <t>status = "sold"</t>
+  </si>
+  <si>
+    <t>Tạo pet với nhiều photoUrls</t>
+  </si>
+  <si>
+    <t>photoUrls là mảng nhiều phần tử</t>
+  </si>
+  <si>
+    <t>Tạo pet với id nhỏ nhất hợp lệ</t>
+  </si>
+  <si>
+    <t>id = 1</t>
+  </si>
+  <si>
+    <t>Tạo pet với id = 0</t>
+  </si>
+  <si>
+    <t>id = 0</t>
+  </si>
+  <si>
+    <t>API trả về 200 hoặc lỗi validate</t>
+  </si>
+  <si>
+    <t>Tạo pet với id âm</t>
+  </si>
+  <si>
+    <t>Tạo pet với id rất lớn</t>
+  </si>
+  <si>
+    <t>Tạo pet với id = Long max</t>
+  </si>
+  <si>
+    <t>id = 9223372036854775807</t>
+  </si>
+  <si>
+    <t>Tạo pet với id vượt quá giới hạn</t>
+  </si>
+  <si>
+    <t>id = 9223372036854775808</t>
+  </si>
+  <si>
+    <t>Tạo pet với name rỗng</t>
+  </si>
+  <si>
+    <t>name = ""</t>
+  </si>
+  <si>
+    <t>Tạo pet với name null</t>
+  </si>
+  <si>
+    <t>name = null</t>
+  </si>
+  <si>
+    <t>Tạo pet với name rất dài (boundary max)</t>
+  </si>
+  <si>
+    <t>name = chuỗi max length</t>
+  </si>
+  <si>
+    <t>Tạo pet với name vượt quá max length</t>
+  </si>
+  <si>
+    <t>name = chuỗi quá dài</t>
+  </si>
+  <si>
+    <t>Tạo pet với id là string</t>
+  </si>
+  <si>
+    <t>Tạo pet với name là số</t>
+  </si>
+  <si>
+    <t>name = 123</t>
+  </si>
+  <si>
+    <t>Tạo pet với status không hợp lệ</t>
+  </si>
+  <si>
+    <t>status = "unknown"</t>
+  </si>
+  <si>
+    <t>[PET20]</t>
+  </si>
+  <si>
+    <t>Tạo pet với photoUrls không phải mảng</t>
+  </si>
+  <si>
+    <t>photoUrls = "url"</t>
+  </si>
+  <si>
+    <t>[PET21]</t>
+  </si>
+  <si>
+    <t>Tạo pet với tags không phải mảng</t>
+  </si>
+  <si>
+    <t>tags = "tag1"</t>
+  </si>
+  <si>
+    <t>[PET22]</t>
+  </si>
+  <si>
+    <t>Thiếu trường name</t>
+  </si>
+  <si>
+    <t>Không có field name</t>
+  </si>
+  <si>
+    <t>[PET23]</t>
+  </si>
+  <si>
+    <t>Thiếu trường id</t>
+  </si>
+  <si>
+    <t>Không có field id</t>
+  </si>
+  <si>
+    <t>API trả về 200 hoặc auto-generate</t>
+  </si>
+  <si>
+    <t>[PET24]</t>
+  </si>
+  <si>
+    <t>Body rỗng</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>[PET25]</t>
+  </si>
+  <si>
+    <t>Body null</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>Cập nhật pet với dữ liệu hợp lệ đầy đủ</t>
+  </si>
+  <si>
+    <t>Pet tồn tại, body hợp lệ (id, name, status,...)</t>
+  </si>
+  <si>
+    <t>1. Gửi request PUT /pet với body hợp lệ</t>
+  </si>
+  <si>
+    <t>API trả về 200 OK, cập nhật thành công</t>
+  </si>
+  <si>
+    <t>Cập nhật pet với dữ liệu tối thiểu</t>
+  </si>
+  <si>
+    <t>Pet tồn tại, chỉ có id và name</t>
+  </si>
+  <si>
+    <t>Cập nhật status = available</t>
+  </si>
+  <si>
+    <t>status hợp lệ</t>
+  </si>
+  <si>
+    <t>Cập nhật status = pending</t>
+  </si>
+  <si>
+    <t>Cập nhật status = sold</t>
+  </si>
+  <si>
+    <t>Cập nhật với nhiều photoUrls</t>
+  </si>
+  <si>
+    <t>photoUrls là mảng hợp lệ</t>
+  </si>
+  <si>
+    <t>Cập nhật pet với ID nhỏ nhất hợp lệ</t>
+  </si>
+  <si>
+    <t>Cập nhật pet với ID = 0</t>
+  </si>
+  <si>
+    <t>Cập nhật pet với ID âm</t>
+  </si>
+  <si>
+    <t>Cập nhật pet với ID rất lớn</t>
+  </si>
+  <si>
+    <t>Cập nhật với ID = Long max</t>
+  </si>
+  <si>
+    <t>Cập nhật với ID vượt giới hạn</t>
+  </si>
+  <si>
+    <t>Cập nhật với name rỗng</t>
+  </si>
+  <si>
+    <t>Cập nhật với name null</t>
+  </si>
+  <si>
+    <t>Cập nhật name đạt max length</t>
+  </si>
+  <si>
+    <t>Cập nhật name vượt max length</t>
+  </si>
+  <si>
+    <t>name quá dài</t>
+  </si>
+  <si>
+    <t>Cập nhật với id dạng string</t>
+  </si>
+  <si>
+    <t>Cập nhật với name dạng số</t>
+  </si>
+  <si>
+    <t>Cập nhật với status không hợp lệ</t>
+  </si>
+  <si>
+    <t>status = "invalid"</t>
+  </si>
+  <si>
+    <t>Cập nhật với photoUrls sai kiểu</t>
+  </si>
+  <si>
+    <t>Cập nhật với tags sai kiểu</t>
+  </si>
+  <si>
+    <t>Thiếu field id khi update</t>
+  </si>
+  <si>
+    <t>Không có id</t>
+  </si>
+  <si>
+    <t>Update pet không tồn tại</t>
+  </si>
+  <si>
+    <t>id không tồn tại</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID hợp lệ và tồn tại</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/10</t>
+  </si>
+  <si>
+    <t>API trả về 200 OK, xóa thành công</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID hợp lệ khác</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/25</t>
+  </si>
+  <si>
+    <t>Xóa pet không tồn tại</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID nhỏ nhất hợp lệ</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/1</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID = 0</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/0</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/-1</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/999999999</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID = Long max</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/{id}</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID vượt giới hạn</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID dạng string số</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/15</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID là chữ</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID chứa chữ và số</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/123abc</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID chứa ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/@#$</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID là số thực</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/1.5</t>
+  </si>
+  <si>
+    <t>Xóa pet với ID là boolean</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/true</t>
+  </si>
+  <si>
+    <t>1. Gửi request DELETE /pet/</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1583,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1048,6 +1592,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1602,139 +2149,139 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="66" spans="1:5">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="49.5" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="85" customHeight="1" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="49.5" spans="1:5">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="33" spans="1:5">
+      <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" ht="66" customHeight="1" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" ht="66" customHeight="1" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" ht="49.5" spans="1:5">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1" spans="1:5">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1775,172 +2322,172 @@
       </c>
     </row>
     <row r="2" ht="49.5" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="3" ht="49.5" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" ht="49.5" spans="1:5">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="33" spans="1:5">
+      <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" ht="49.5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="33" spans="1:5">
+      <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" ht="49.5" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="33" spans="1:5">
+      <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" ht="49.5" spans="1:5">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" ht="49.5" spans="1:5">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="33" spans="1:5">
+      <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" ht="49.5" spans="1:5">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" ht="49.5" spans="1:5">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="33" spans="1:5">
+      <c r="A10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" ht="49.5" spans="1:5">
-      <c r="A11" s="3" t="s">
+    <row r="11" ht="33" spans="1:5">
+      <c r="A11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1982,138 +2529,138 @@
       </c>
     </row>
     <row r="2" ht="61" customHeight="1" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" ht="41" customHeight="1" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="4" ht="41" customHeight="1" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="5" ht="41" customHeight="1" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="6" ht="41" customHeight="1" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="7" ht="41" customHeight="1" spans="1:5">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8" ht="41" customHeight="1" spans="1:5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="9" ht="41" customHeight="1" spans="1:5">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2137,7 +2684,7 @@
     <col min="6" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" spans="1:5">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2154,106 +2701,1729 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="66" spans="1:5">
+    <row r="2" ht="49.5" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" ht="33" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" ht="33" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" ht="33" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" ht="33" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" ht="61" customHeight="1" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="12.5454545454545" style="1" customWidth="1"/>
+    <col min="2" max="5" width="23.8181818181818" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.72727272727273" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="32" customHeight="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="85" customHeight="1" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" ht="49.5" spans="1:5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" spans="1:5">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" ht="49.5" spans="1:5">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="66" customHeight="1" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" ht="49.5" spans="1:5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="66" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" ht="49.5" spans="1:5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="33" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" ht="61" customHeight="1" spans="1:5">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="58" customHeight="1" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="58" customHeight="1" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" ht="33" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" ht="33" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" ht="49.5" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" ht="33" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" ht="33" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" ht="33" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" ht="33" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" ht="33" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" ht="33" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" ht="33" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" ht="33" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" ht="33" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="11.4545454545455" style="1" customWidth="1"/>
+    <col min="2" max="3" width="20.3636363636364" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.4545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.3636363636364" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.72727272727273" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="66" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" ht="33" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" ht="49.5" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" ht="49.5" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" ht="33" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" ht="33" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" ht="49.5" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" ht="33" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" ht="33" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" ht="33" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" ht="33" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" ht="49.5" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" ht="33" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" ht="33" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" ht="33" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="25" ht="33" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" ht="33" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="12.3636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.4545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6363636363636" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.3636363636364" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.1818181818182" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.72727272727273" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="35" customHeight="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="41" customHeight="1" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="41" customHeight="1" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="41" customHeight="1" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="41" customHeight="1" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="41" customHeight="1" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="41" customHeight="1" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="41" customHeight="1" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" ht="33" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" ht="33" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" ht="33" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" ht="33" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" ht="33" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" ht="33" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" ht="33" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" ht="33" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" ht="33" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" ht="33" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" ht="33" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" ht="33" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" ht="33" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" ht="33" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" ht="33" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" ht="33" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" ht="33" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" ht="33" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.0909090909091" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7272727272727" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.9090909090909" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6363636363636" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.72727272727273" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="33" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="61" customHeight="1" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" ht="33" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" ht="33" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>85</v>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" ht="49.5" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" ht="49.5" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" ht="33" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" ht="33" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" ht="33" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" ht="49.5" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" ht="33" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" ht="33" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" ht="33" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" ht="33" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" ht="33" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
